--- a/templates/Unit_Test_Plan_Filled.xlsx
+++ b/templates/Unit_Test_Plan_Filled.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bc20060aec94d36e/Desktop/Multi-AI-Agent-Coding-Assistant/templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bc20060aec94d36e/Desktop/Multi-AI-Agent-Coding-Assistant - Copy(freebuff)/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_EC6CC44CF3BCB99BC811487D28D304D83B3C6462" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63F26C66-0DB2-423B-8A77-7A80A5C99340}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_4F6DF0643C42D0055C65FF212A699F98B7A5A8A3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C69E7E3-7A4E-4993-BDF3-4657D03BC30E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="193">
   <si>
     <t>Sl: No:</t>
   </si>
@@ -395,6 +395,210 @@
   </si>
   <si>
     <t>Validation message displayed successfully.</t>
+  </si>
+  <si>
+    <t>TC-021</t>
+  </si>
+  <si>
+    <t>Quick Actions</t>
+  </si>
+  <si>
+    <t>Ask-first flow</t>
+  </si>
+  <si>
+    <t>Click each quick action.</t>
+  </si>
+  <si>
+    <t>A question prompt appears and nothing runs until the user types.</t>
+  </si>
+  <si>
+    <t>Quick actions ask first, no auto-submit.</t>
+  </si>
+  <si>
+    <t>TC-022</t>
+  </si>
+  <si>
+    <t>Upload Dedupe</t>
+  </si>
+  <si>
+    <t>Duplicate upload</t>
+  </si>
+  <si>
+    <t>Upload the same file twice.</t>
+  </si>
+  <si>
+    <t>Only one entry in My Files.</t>
+  </si>
+  <si>
+    <t>File appears exactly once.</t>
+  </si>
+  <si>
+    <t>TC-023</t>
+  </si>
+  <si>
+    <t>File Routing</t>
+  </si>
+  <si>
+    <t>Analyse it</t>
+  </si>
+  <si>
+    <t>Attach a file and send 'analyse it'.</t>
+  </si>
+  <si>
+    <t>Routed to Code Analysis Agent.</t>
+  </si>
+  <si>
+    <t>Analysis performed on the attached file.</t>
+  </si>
+  <si>
+    <t>TC-024</t>
+  </si>
+  <si>
+    <t>Review it</t>
+  </si>
+  <si>
+    <t>Attach a file and send 'review it'.</t>
+  </si>
+  <si>
+    <t>Review performed on the attached file.</t>
+  </si>
+  <si>
+    <t>TC-025</t>
+  </si>
+  <si>
+    <t>Attach a file and send 'generate documentation'.</t>
+  </si>
+  <si>
+    <t>Routed to Documentation Agent.</t>
+  </si>
+  <si>
+    <t>Documentation generated from the attached file.</t>
+  </si>
+  <si>
+    <t>TC-026</t>
+  </si>
+  <si>
+    <t>Analytics KPIs</t>
+  </si>
+  <si>
+    <t>Exact numbers</t>
+  </si>
+  <si>
+    <t>Open Analytics with no executions.</t>
+  </si>
+  <si>
+    <t>Success rate shows 0%, conversations count real chats only.</t>
+  </si>
+  <si>
+    <t>Dashboard numbers are exact.</t>
+  </si>
+  <si>
+    <t>TC-027</t>
+  </si>
+  <si>
+    <t>Files Page</t>
+  </si>
+  <si>
+    <t>Single save</t>
+  </si>
+  <si>
+    <t>Upload a file on My Files and rerun the page.</t>
+  </si>
+  <si>
+    <t>The file is saved exactly once.</t>
+  </si>
+  <si>
+    <t>No duplicate entries created.</t>
+  </si>
+  <si>
+    <t>TC-028</t>
+  </si>
+  <si>
+    <t>Chat History</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>Search past conversations and messages.</t>
+  </si>
+  <si>
+    <t>Matching chats and message hits listed.</t>
+  </si>
+  <si>
+    <t>Search works correctly.</t>
+  </si>
+  <si>
+    <t>TC-029</t>
+  </si>
+  <si>
+    <t>Conversation Export</t>
+  </si>
+  <si>
+    <t>Export</t>
+  </si>
+  <si>
+    <t>Export a single conversation from Chat History.</t>
+  </si>
+  <si>
+    <t>Conversation downloads as a file.</t>
+  </si>
+  <si>
+    <t>Export verified successfully.</t>
+  </si>
+  <si>
+    <t>TC-030</t>
+  </si>
+  <si>
+    <t>Legal Pages</t>
+  </si>
+  <si>
+    <t>Render</t>
+  </si>
+  <si>
+    <t>Open Terms, Privacy, Help and What's new.</t>
+  </si>
+  <si>
+    <t>Each page renders without errors.</t>
+  </si>
+  <si>
+    <t>Legal pages render correctly.</t>
+  </si>
+  <si>
+    <t>TC-031</t>
+  </si>
+  <si>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>Dark-only + English</t>
+  </si>
+  <si>
+    <t>Open Settings and try to change theme/language.</t>
+  </si>
+  <si>
+    <t>Only text size and other preferences available.</t>
+  </si>
+  <si>
+    <t>App stays dark and in English.</t>
+  </si>
+  <si>
+    <t>TC-032</t>
+  </si>
+  <si>
+    <t>Uploader Reset</t>
+  </si>
+  <si>
+    <t>No errors</t>
+  </si>
+  <si>
+    <t>Upload a file, send a message, then upload again.</t>
+  </si>
+  <si>
+    <t>No Streamlit exceptions; files not re-saved.</t>
+  </si>
+  <si>
+    <t>Uploader resets cleanly.</t>
   </si>
 </sst>
 </file>
@@ -789,15 +993,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
     <col min="2" max="2" width="19.88671875" customWidth="1"/>
     <col min="3" max="3" width="20.21875" customWidth="1"/>
-    <col min="4" max="4" width="25.88671875" customWidth="1"/>
-    <col min="5" max="5" width="24.109375" customWidth="1"/>
-    <col min="6" max="6" width="36.33203125" customWidth="1"/>
+    <col min="4" max="4" width="41.5546875" customWidth="1"/>
+    <col min="5" max="5" width="53.77734375" customWidth="1"/>
+    <col min="6" max="6" width="42.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -920,7 +1124,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>36</v>
       </c>
@@ -940,7 +1144,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>42</v>
       </c>
@@ -960,7 +1164,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>48</v>
       </c>
@@ -980,7 +1184,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>54</v>
       </c>
@@ -1000,7 +1204,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>60</v>
       </c>
@@ -1020,7 +1224,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>66</v>
       </c>
@@ -1040,7 +1244,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>72</v>
       </c>
@@ -1060,7 +1264,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>78</v>
       </c>
@@ -1080,7 +1284,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>84</v>
       </c>
@@ -1100,7 +1304,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>90</v>
       </c>
@@ -1120,7 +1324,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>96</v>
       </c>
@@ -1140,7 +1344,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>102</v>
       </c>
@@ -1160,7 +1364,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>108</v>
       </c>
@@ -1180,7 +1384,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>114</v>
       </c>
@@ -1200,7 +1404,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>119</v>
       </c>
@@ -1218,6 +1422,246 @@
       </c>
       <c r="F21" s="3" t="s">
         <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F22" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" t="s">
+        <v>132</v>
+      </c>
+      <c r="C23" t="s">
+        <v>133</v>
+      </c>
+      <c r="D23" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F23" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" t="s">
+        <v>139</v>
+      </c>
+      <c r="D24" t="s">
+        <v>140</v>
+      </c>
+      <c r="E24" t="s">
+        <v>141</v>
+      </c>
+      <c r="F24" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>143</v>
+      </c>
+      <c r="B25" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" t="s">
+        <v>145</v>
+      </c>
+      <c r="E25" t="s">
+        <v>141</v>
+      </c>
+      <c r="F25" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
+        <v>148</v>
+      </c>
+      <c r="E26" t="s">
+        <v>149</v>
+      </c>
+      <c r="F26" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C27" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" t="s">
+        <v>154</v>
+      </c>
+      <c r="E27" t="s">
+        <v>155</v>
+      </c>
+      <c r="F27" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C28" t="s">
+        <v>159</v>
+      </c>
+      <c r="D28" t="s">
+        <v>160</v>
+      </c>
+      <c r="E28" t="s">
+        <v>161</v>
+      </c>
+      <c r="F28" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>163</v>
+      </c>
+      <c r="B29" t="s">
+        <v>164</v>
+      </c>
+      <c r="C29" t="s">
+        <v>165</v>
+      </c>
+      <c r="D29" t="s">
+        <v>166</v>
+      </c>
+      <c r="E29" t="s">
+        <v>167</v>
+      </c>
+      <c r="F29" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>169</v>
+      </c>
+      <c r="B30" t="s">
+        <v>170</v>
+      </c>
+      <c r="C30" t="s">
+        <v>171</v>
+      </c>
+      <c r="D30" t="s">
+        <v>172</v>
+      </c>
+      <c r="E30" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>175</v>
+      </c>
+      <c r="B31" t="s">
+        <v>176</v>
+      </c>
+      <c r="C31" t="s">
+        <v>177</v>
+      </c>
+      <c r="D31" t="s">
+        <v>178</v>
+      </c>
+      <c r="E31" t="s">
+        <v>179</v>
+      </c>
+      <c r="F31" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B32" t="s">
+        <v>182</v>
+      </c>
+      <c r="C32" t="s">
+        <v>183</v>
+      </c>
+      <c r="D32" t="s">
+        <v>184</v>
+      </c>
+      <c r="E32" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>187</v>
+      </c>
+      <c r="B33" t="s">
+        <v>188</v>
+      </c>
+      <c r="C33" t="s">
+        <v>189</v>
+      </c>
+      <c r="D33" t="s">
+        <v>190</v>
+      </c>
+      <c r="E33" t="s">
+        <v>191</v>
+      </c>
+      <c r="F33" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/templates/Unit_Test_Plan_Filled.xlsx
+++ b/templates/Unit_Test_Plan_Filled.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bc20060aec94d36e/Desktop/Multi-AI-Agent-Coding-Assistant - Copy(freebuff)/templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bc20060aec94d36e/Desktop/Multi-AI-Agent-Coding-Assistant/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_4F6DF0643C42D0055C65FF212A699F98B7A5A8A3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C69E7E3-7A4E-4993-BDF3-4657D03BC30E}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_4F6DF064764290245665FFF2322CBDE0B6A5BCCD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5A6E211-2907-4349-A2B9-89C30FADC98B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="259">
   <si>
     <t>Sl: No:</t>
   </si>
@@ -599,6 +599,204 @@
   </si>
   <si>
     <t>Uploader resets cleanly.</t>
+  </si>
+  <si>
+    <t>TC-033</t>
+  </si>
+  <si>
+    <t>Google Sign-In</t>
+  </si>
+  <si>
+    <t>Sign-in flow</t>
+  </si>
+  <si>
+    <t>Click Continue with Google, complete OAuth, return to the app.</t>
+  </si>
+  <si>
+    <t>User is authenticated in the application UI.</t>
+  </si>
+  <si>
+    <t>Google sign-in works end to end.</t>
+  </si>
+  <si>
+    <t>TC-034</t>
+  </si>
+  <si>
+    <t>Project ZIP first turn</t>
+  </si>
+  <si>
+    <t>Analyze project</t>
+  </si>
+  <si>
+    <t>Upload a project ZIP and ask 'Analyze this project'.</t>
+  </si>
+  <si>
+    <t>Project Analyzer reads the actual uploaded files.</t>
+  </si>
+  <si>
+    <t>Real analysis of the uploaded ZIP archive generated.</t>
+  </si>
+  <si>
+    <t>TC-035</t>
+  </si>
+  <si>
+    <t>Project vs code routing</t>
+  </si>
+  <si>
+    <t>Subject routing</t>
+  </si>
+  <si>
+    <t>Ask 'Analyze this project' then 'Analyze this Python code'.</t>
+  </si>
+  <si>
+    <t>Project Analyzer / Code Analysis respectively.</t>
+  </si>
+  <si>
+    <t>Both route to the correct agent.</t>
+  </si>
+  <si>
+    <t>TC-036</t>
+  </si>
+  <si>
+    <t>No-ZIP safety</t>
+  </si>
+  <si>
+    <t>Missing project</t>
+  </si>
+  <si>
+    <t>Ask 'Review this project' with no project uploaded.</t>
+  </si>
+  <si>
+    <t>Friendly upload prompt; no workspace scan.</t>
+  </si>
+  <si>
+    <t>Upload prompt shown, workspace untouched.</t>
+  </si>
+  <si>
+    <t>TC-037</t>
+  </si>
+  <si>
+    <t>Error-handling follow-up</t>
+  </si>
+  <si>
+    <t>Debug context</t>
+  </si>
+  <si>
+    <t>Debug divide() then send 'Also handle invalid non-numeric input.'.</t>
+  </si>
+  <si>
+    <t>Debugging Agent with the previous code kept.</t>
+  </si>
+  <si>
+    <t>Debugging Agent, divide() context retained.</t>
+  </si>
+  <si>
+    <t>TC-038</t>
+  </si>
+  <si>
+    <t>Planner follow-up</t>
+  </si>
+  <si>
+    <t>Plan context</t>
+  </si>
+  <si>
+    <t>Create a plan then 'Break step 3 into smaller implementation tasks.'.</t>
+  </si>
+  <si>
+    <t>Planner Agent with the plan context kept.</t>
+  </si>
+  <si>
+    <t>Planner Agent, plan context retained.</t>
+  </si>
+  <si>
+    <t>TC-039</t>
+  </si>
+  <si>
+    <t>Think-block strip</t>
+  </si>
+  <si>
+    <t>Output sanitisation</t>
+  </si>
+  <si>
+    <t>Model returns &lt;think&gt;...&lt;/think&gt; plus an answer.</t>
+  </si>
+  <si>
+    <t>Only the answer is shown; reasoning hidden.</t>
+  </si>
+  <si>
+    <t>Think blocks removed from all responses.</t>
+  </si>
+  <si>
+    <t>TC-040</t>
+  </si>
+  <si>
+    <t>Static metrics</t>
+  </si>
+  <si>
+    <t>Metrics default</t>
+  </si>
+  <si>
+    <t>Ask 'Analyze this code' then 'Give me the static metrics'.</t>
+  </si>
+  <si>
+    <t>Metrics hidden unless explicitly requested.</t>
+  </si>
+  <si>
+    <t>Hidden by default; shown only on request.</t>
+  </si>
+  <si>
+    <t>TC-041</t>
+  </si>
+  <si>
+    <t>Table overflow</t>
+  </si>
+  <si>
+    <t>UI layout</t>
+  </si>
+  <si>
+    <t>Render a wide markdown table in chat.</t>
+  </si>
+  <si>
+    <t>Table stays inside the chat container.</t>
+  </si>
+  <si>
+    <t>No horizontal overflow.</t>
+  </si>
+  <si>
+    <t>TC-042</t>
+  </si>
+  <si>
+    <t>+ menu</t>
+  </si>
+  <si>
+    <t>Attachment menu</t>
+  </si>
+  <si>
+    <t>Open the + menu in a fresh chat.</t>
+  </si>
+  <si>
+    <t>Upload File plus actions only; no redundant upload buttons.</t>
+  </si>
+  <si>
+    <t>Clean menu verified.</t>
+  </si>
+  <si>
+    <t>TC-043</t>
+  </si>
+  <si>
+    <t>Full regression suite</t>
+  </si>
+  <si>
+    <t>All tests</t>
+  </si>
+  <si>
+    <t>Run the complete test suite.</t>
+  </si>
+  <si>
+    <t>All tests pass.</t>
+  </si>
+  <si>
+    <t>276 tests passed, 0 failed.</t>
   </si>
 </sst>
 </file>
@@ -690,10 +888,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -993,13 +1187,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
     <col min="2" max="2" width="19.88671875" customWidth="1"/>
     <col min="3" max="3" width="20.21875" customWidth="1"/>
-    <col min="4" max="4" width="41.5546875" customWidth="1"/>
+    <col min="4" max="4" width="57.77734375" customWidth="1"/>
     <col min="5" max="5" width="53.77734375" customWidth="1"/>
     <col min="6" max="6" width="42.21875" customWidth="1"/>
   </cols>
@@ -1664,6 +1858,226 @@
         <v>192</v>
       </c>
     </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>193</v>
+      </c>
+      <c r="B34" t="s">
+        <v>194</v>
+      </c>
+      <c r="C34" t="s">
+        <v>195</v>
+      </c>
+      <c r="D34" t="s">
+        <v>196</v>
+      </c>
+      <c r="E34" t="s">
+        <v>197</v>
+      </c>
+      <c r="F34" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>199</v>
+      </c>
+      <c r="B35" t="s">
+        <v>200</v>
+      </c>
+      <c r="C35" t="s">
+        <v>201</v>
+      </c>
+      <c r="D35" t="s">
+        <v>202</v>
+      </c>
+      <c r="E35" t="s">
+        <v>203</v>
+      </c>
+      <c r="F35" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>205</v>
+      </c>
+      <c r="B36" t="s">
+        <v>206</v>
+      </c>
+      <c r="C36" t="s">
+        <v>207</v>
+      </c>
+      <c r="D36" t="s">
+        <v>208</v>
+      </c>
+      <c r="E36" t="s">
+        <v>209</v>
+      </c>
+      <c r="F36" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>211</v>
+      </c>
+      <c r="B37" t="s">
+        <v>212</v>
+      </c>
+      <c r="C37" t="s">
+        <v>213</v>
+      </c>
+      <c r="D37" t="s">
+        <v>214</v>
+      </c>
+      <c r="E37" t="s">
+        <v>215</v>
+      </c>
+      <c r="F37" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>217</v>
+      </c>
+      <c r="B38" t="s">
+        <v>218</v>
+      </c>
+      <c r="C38" t="s">
+        <v>219</v>
+      </c>
+      <c r="D38" t="s">
+        <v>220</v>
+      </c>
+      <c r="E38" t="s">
+        <v>221</v>
+      </c>
+      <c r="F38" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>223</v>
+      </c>
+      <c r="B39" t="s">
+        <v>224</v>
+      </c>
+      <c r="C39" t="s">
+        <v>225</v>
+      </c>
+      <c r="D39" t="s">
+        <v>226</v>
+      </c>
+      <c r="E39" t="s">
+        <v>227</v>
+      </c>
+      <c r="F39" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>229</v>
+      </c>
+      <c r="B40" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" t="s">
+        <v>231</v>
+      </c>
+      <c r="D40" t="s">
+        <v>232</v>
+      </c>
+      <c r="E40" t="s">
+        <v>233</v>
+      </c>
+      <c r="F40" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>235</v>
+      </c>
+      <c r="B41" t="s">
+        <v>236</v>
+      </c>
+      <c r="C41" t="s">
+        <v>237</v>
+      </c>
+      <c r="D41" t="s">
+        <v>238</v>
+      </c>
+      <c r="E41" t="s">
+        <v>239</v>
+      </c>
+      <c r="F41" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>241</v>
+      </c>
+      <c r="B42" t="s">
+        <v>242</v>
+      </c>
+      <c r="C42" t="s">
+        <v>243</v>
+      </c>
+      <c r="D42" t="s">
+        <v>244</v>
+      </c>
+      <c r="E42" t="s">
+        <v>245</v>
+      </c>
+      <c r="F42" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>247</v>
+      </c>
+      <c r="B43" t="s">
+        <v>248</v>
+      </c>
+      <c r="C43" t="s">
+        <v>249</v>
+      </c>
+      <c r="D43" t="s">
+        <v>250</v>
+      </c>
+      <c r="E43" t="s">
+        <v>251</v>
+      </c>
+      <c r="F43" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>253</v>
+      </c>
+      <c r="B44" t="s">
+        <v>254</v>
+      </c>
+      <c r="C44" t="s">
+        <v>255</v>
+      </c>
+      <c r="D44" t="s">
+        <v>256</v>
+      </c>
+      <c r="E44" t="s">
+        <v>257</v>
+      </c>
+      <c r="F44" t="s">
+        <v>258</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
